--- a/Deliverable/Interface_Board/BOM/(5 Boards)Digikey-Interface-Board-BOM.xlsx
+++ b/Deliverable/Interface_Board/BOM/(5 Boards)Digikey-Interface-Board-BOM.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GrantKros-CoopMonitor\Deliverable\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GrantKros-CoopMonitor\Deliverable\Interface_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E777637-341F-41EE-87D2-32D123000F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2259E5FF-C5BF-4D02-BD9C-6730B29894D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Interface Board " sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -32,9 +32,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="73">
   <si>
-    <t>Bill of Material (BOM) for Grant</t>
-  </si>
-  <si>
     <t>S. No.</t>
   </si>
   <si>
@@ -249,6 +246,9 @@
   </si>
   <si>
     <t>Connector</t>
+  </si>
+  <si>
+    <t>Bill of Material (BOM) for Grant Interface Board</t>
   </si>
 </sst>
 </file>
@@ -256,9 +256,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.0000_);[Red]\(&quot;$&quot;#,##0.0000\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000_);[Red]\(&quot;$&quot;#,##0.0000\)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -335,6 +335,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -747,7 +762,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -769,10 +784,130 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -799,127 +934,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1219,507 +1249,507 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="10"/>
+      <c r="A1" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="49"/>
+      <c r="O1" s="50"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="M2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="D3" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="E3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="F3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="G3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="H3" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="I3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="20">
+      <c r="J3" s="11">
         <v>5</v>
       </c>
-      <c r="K3" s="21">
+      <c r="K3" s="12">
         <f>J3*5</f>
         <v>25</v>
       </c>
-      <c r="L3" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="23">
+      <c r="L3" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="14">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="14">
         <f>M3*K3</f>
         <v>0.72500000000000009</v>
       </c>
-      <c r="O3" s="24"/>
+      <c r="O3" s="15"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="25" t="s">
+      <c r="B4" s="54"/>
+      <c r="C4" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="E4" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="26" t="s">
+      <c r="G4" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="H4" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="27">
+      <c r="J4" s="18">
         <v>2</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="19">
         <f t="shared" ref="K4:K11" si="0">J4*5</f>
         <v>10</v>
       </c>
-      <c r="L4" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" s="30">
+      <c r="L4" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="21">
         <v>0.08</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="21">
         <f t="shared" ref="N4:N11" si="1">M4*K4</f>
         <v>0.8</v>
       </c>
-      <c r="O4" s="31"/>
+      <c r="O4" s="22"/>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="4">
         <v>3</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="25" t="s">
+      <c r="B5" s="54"/>
+      <c r="C5" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="58" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="E5" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="26" t="s">
+      <c r="G5" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="H5" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" s="27">
+      <c r="J5" s="18">
         <v>1</v>
       </c>
-      <c r="K5" s="28">
+      <c r="K5" s="19">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L5" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="30">
+      <c r="L5" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="21">
         <v>0.156</v>
       </c>
-      <c r="N5" s="30">
+      <c r="N5" s="21">
         <f t="shared" si="1"/>
         <v>0.78</v>
       </c>
-      <c r="O5" s="31"/>
+      <c r="O5" s="22"/>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="32" t="s">
+      <c r="B6" s="55"/>
+      <c r="C6" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="E6" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="F6" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="G6" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="34" t="s">
+      <c r="H6" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="J6" s="35">
+      <c r="J6" s="26">
         <v>1</v>
       </c>
-      <c r="K6" s="36">
+      <c r="K6" s="27">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L6" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" s="38">
+      <c r="L6" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" s="29">
         <v>0.38</v>
       </c>
-      <c r="N6" s="38">
+      <c r="N6" s="29">
         <f t="shared" si="1"/>
         <v>1.9</v>
       </c>
-      <c r="O6" s="39"/>
+      <c r="O6" s="30"/>
     </row>
     <row r="7" spans="1:15" ht="25.5">
       <c r="A7" s="4">
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="40" t="s">
+      <c r="D7" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="E7" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="F7" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="G7" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="42">
+      <c r="H7" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="33">
         <v>4</v>
       </c>
-      <c r="K7" s="43">
+      <c r="K7" s="34">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="L7" s="56" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="57">
+      <c r="L7" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" s="48">
         <v>0.48599999999999999</v>
       </c>
-      <c r="N7" s="38">
+      <c r="N7" s="29">
         <f t="shared" si="1"/>
         <v>9.7199999999999989</v>
       </c>
-      <c r="O7" s="44"/>
+      <c r="O7" s="35"/>
     </row>
     <row r="8" spans="1:15" s="1" customFormat="1">
       <c r="A8" s="4">
         <v>6</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="D8" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="E8" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="F8" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="45" t="s">
+      <c r="G8" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="H8" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="I8" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="J8" s="20">
+      <c r="J8" s="11">
         <v>3</v>
       </c>
-      <c r="K8" s="21">
+      <c r="K8" s="12">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="L8" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="M8" s="23">
+      <c r="L8" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="M8" s="14">
         <v>1.6E-2</v>
       </c>
-      <c r="N8" s="23">
+      <c r="N8" s="14">
         <f t="shared" si="1"/>
         <v>0.24</v>
       </c>
-      <c r="O8" s="24"/>
+      <c r="O8" s="15"/>
     </row>
     <row r="9" spans="1:15" ht="25.5">
       <c r="A9" s="4">
         <v>7</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="46" t="s">
+      <c r="B9" s="55"/>
+      <c r="C9" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="E9" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="F9" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="47" t="s">
+      <c r="G9" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="H9" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="35" t="s">
+      <c r="I9" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="J9" s="35">
+      <c r="J9" s="26">
         <v>1</v>
       </c>
-      <c r="K9" s="36">
+      <c r="K9" s="27">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L9" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" s="38">
+      <c r="L9" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="M9" s="29">
         <v>0.1</v>
       </c>
-      <c r="N9" s="38">
+      <c r="N9" s="29">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="O9" s="39"/>
+      <c r="O9" s="30"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="4">
         <v>8</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="48" t="s">
+      <c r="B10" s="56" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="49" t="s">
+      <c r="E10" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="49" t="s">
+      <c r="G10" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="H10" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="50">
+      <c r="H10" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="41">
         <v>1</v>
       </c>
-      <c r="K10" s="51">
+      <c r="K10" s="42">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L10" s="52" t="s">
-        <v>24</v>
-      </c>
-      <c r="M10" s="53">
+      <c r="L10" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" s="44">
         <v>0.46</v>
       </c>
-      <c r="N10" s="53">
+      <c r="N10" s="44">
         <f t="shared" si="1"/>
         <v>2.3000000000000003</v>
       </c>
-      <c r="O10" s="54"/>
+      <c r="O10" s="45"/>
     </row>
     <row r="11" spans="1:15" ht="25.5">
       <c r="A11" s="4">
         <v>9</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="46" t="s">
+      <c r="B11" s="55"/>
+      <c r="C11" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="E11" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="E11" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="35">
+      <c r="G11" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="26">
         <v>1</v>
       </c>
-      <c r="K11" s="36">
+      <c r="K11" s="27">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L11" s="55" t="s">
-        <v>69</v>
-      </c>
-      <c r="M11" s="38">
+      <c r="L11" s="46" t="s">
+        <v>68</v>
+      </c>
+      <c r="M11" s="29">
         <v>1.1499999999999999</v>
       </c>
-      <c r="N11" s="38">
+      <c r="N11" s="29">
         <f t="shared" si="1"/>
         <v>5.75</v>
       </c>
-      <c r="O11" s="39"/>
+      <c r="O11" s="30"/>
     </row>
     <row r="12" spans="1:15" ht="18.75">
-      <c r="G12" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
+      <c r="G12" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="51"/>
       <c r="N12" s="7">
         <f>SUM(N3:N11)</f>
         <v>22.715</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="18.75">
-      <c r="G13" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
+      <c r="G13" s="52" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="52"/>
       <c r="N13" s="7">
         <f>N12/5</f>
         <v>4.5430000000000001</v>
